--- a/data-manipulation-scripts/sheets-cleanup/sheets/EMBREAGEM COMPLETA 05_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/EMBREAGEM COMPLETA 05_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -28,7 +28,7 @@
     <t>7899248112384</t>
   </si>
   <si>
-    <t>EMBREAGEM COMPLETA  TA GP TITAN FAN CG150 1103318</t>
+    <t>EMBREAGEM COMPLETA  GP TITAN FAN CG150 1103318</t>
   </si>
   <si>
     <t>7899248166332</t>
@@ -217,26 +217,20 @@
     <t>7895099123500</t>
   </si>
   <si>
-    <t>EMBREAGEM COMPLETA IRON YBR125026039</t>
+    <t>EMBREAGEM COMPLETA IRON YBR125 026039</t>
   </si>
   <si>
     <t>0751320981172</t>
   </si>
   <si>
     <t>EMBREAGEM COMPLETA IRON YES125 178767</t>
-  </si>
-  <si>
-    <t>7898635122456</t>
-  </si>
-  <si>
-    <t>EMBREAGEM COMPLETA CAUW PCX 2019</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -248,23 +242,13 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1CD"/>
-        <bgColor rgb="FFB7E1CD"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -273,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -288,15 +272,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,7 +543,9 @@
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -580,7 +557,9 @@
       <c r="C4" s="2">
         <v>2.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
@@ -590,7 +569,9 @@
       <c r="C5" s="2">
         <v>4.0</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="2">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -616,7 +597,9 @@
       <c r="C7" s="2">
         <v>1.0</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -642,7 +625,9 @@
       <c r="C9" s="2">
         <v>2.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -654,7 +639,9 @@
       <c r="C10" s="2">
         <v>2.0</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="2">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -666,7 +653,9 @@
       <c r="C11" s="2">
         <v>2.0</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -678,7 +667,9 @@
       <c r="C12" s="2">
         <v>1.0</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
@@ -704,7 +695,9 @@
       <c r="C14" s="2">
         <v>1.0</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="2">
+        <v>200.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -726,7 +719,9 @@
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
@@ -738,7 +733,9 @@
       <c r="C17" s="2">
         <v>1.0</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
@@ -750,7 +747,9 @@
       <c r="C18" s="2">
         <v>2.0</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
@@ -763,7 +762,7 @@
         <v>2.0</v>
       </c>
       <c r="D19" s="2">
-        <v>150.0</v>
+        <v>190.0</v>
       </c>
     </row>
     <row r="20">
@@ -776,7 +775,9 @@
       <c r="C20" s="2">
         <v>5.0</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
@@ -802,7 +803,9 @@
       <c r="C22" s="2">
         <v>1.0</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="2">
+        <v>250.0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
@@ -912,7 +915,9 @@
       <c r="C30" s="2">
         <v>3.0</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="2">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
@@ -966,7 +971,9 @@
       <c r="C34" s="2">
         <v>1.0</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="2">
+        <v>260.0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
@@ -978,7 +985,9 @@
       <c r="C35" s="2">
         <v>1.0</v>
       </c>
-      <c r="D35" s="4"/>
+      <c r="D35" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
@@ -995,38 +1004,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="7"/>
-      <c r="Y37" s="7"/>
-      <c r="Z37" s="7"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
     </row>
     <row r="38">
       <c r="A38" s="3"/>
@@ -6800,20 +6781,14 @@
       <c r="C999" s="4"/>
       <c r="D999" s="4"/>
     </row>
-    <row r="1000">
-      <c r="A1000" s="3"/>
-      <c r="B1000" s="4"/>
-      <c r="C1000" s="4"/>
-      <c r="D1000" s="4"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1000">
+  <conditionalFormatting sqref="A1:A999">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1000">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A999">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
